--- a/src/attributions/attributions_saliency_traj_242.xlsx
+++ b/src/attributions/attributions_saliency_traj_242.xlsx
@@ -999,1709 +999,1709 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.372522717701941e-08</v>
+        <v>9.806602975004353e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>6.267542289606354e-07</v>
+        <v>2.26012161874678e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.890912670887701e-07</v>
+        <v>2.59710986938444e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.280558248912712e-07</v>
+        <v>1.581884862389416e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.468536225956996e-08</v>
+        <v>1.750009869283531e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.599067319257301e-07</v>
+        <v>3.058687070733868e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.990183875477669e-07</v>
+        <v>6.232402483874466e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>2.297793173511309e-07</v>
+        <v>1.61583666340448e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.142173431389892e-07</v>
+        <v>1.001682358037215e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>6.047161349442831e-08</v>
+        <v>1.136002902057953e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>4.318595756558352e-07</v>
+        <v>3.286556602688506e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.254634298675228e-07</v>
+        <v>1.154567144112661e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>7.225396814192209e-08</v>
+        <v>2.665288229763974e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.519711645414645e-07</v>
+        <v>2.812542697938625e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>3.800916203999805e-07</v>
+        <v>3.908007056452334e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.243957197833879e-07</v>
+        <v>3.851317160297185e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.29040955698656e-07</v>
+        <v>1.187346970255021e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>8.695761266608315e-08</v>
+        <v>1.524037816125201e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>7.197863993724241e-08</v>
+        <v>1.65885103342589e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>2.952361555230709e-08</v>
+        <v>8.399112630286254e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29504336143782e-08</v>
+        <v>3.89824299418251e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.343116196039773e-07</v>
+        <v>8.918520506995264e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.348574585335882e-07</v>
+        <v>5.352146217774134e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>5.787547863178588e-08</v>
+        <v>8.045304639381357e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.225852344077794e-07</v>
+        <v>2.498312028365035e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.139931964961761e-08</v>
+        <v>5.575921477429802e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.845566247193346e-08</v>
+        <v>6.904082852088322e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.040688886178032e-07</v>
+        <v>8.161111509252805e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.390756754204858e-08</v>
+        <v>4.443196758074919e-06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.259964221844712e-07</v>
+        <v>3.231721848351299e-06</v>
       </c>
       <c r="AE2" t="n">
-        <v>6.098319005332087e-08</v>
+        <v>6.129449047875823e-06</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.34586900407885e-08</v>
+        <v>1.633768624742515e-05</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.738972047060088e-08</v>
+        <v>8.644858098705299e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.903409151462256e-08</v>
+        <v>5.918551323702559e-06</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.017306309833657e-08</v>
+        <v>6.501772077172063e-06</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4.519061747032538e-08</v>
+        <v>7.874180482758675e-06</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.646661900167601e-07</v>
+        <v>3.028869286936242e-06</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.316490548854745e-08</v>
+        <v>1.01962450571591e-05</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.231409356705626e-07</v>
+        <v>1.263719013877562e-06</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.64562282584302e-08</v>
+        <v>8.067096132435836e-06</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.688871596021272e-08</v>
+        <v>5.482243068399839e-06</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.529221265172964e-07</v>
+        <v>1.102493297366891e-05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.213361855434414e-08</v>
+        <v>5.253697281659697e-07</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.364428876779129e-08</v>
+        <v>6.221721378096845e-06</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.053562570518807e-08</v>
+        <v>4.422873189469101e-06</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.690654727326546e-09</v>
+        <v>9.055520422407426e-07</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.000959338805842e-07</v>
+        <v>6.090189344831742e-05</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.72409869492185e-07</v>
+        <v>7.097027719282778e-06</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.268249576469316e-07</v>
+        <v>9.219750609190669e-06</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.056105674024366e-07</v>
+        <v>7.886232197051868e-06</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.011466216979898e-07</v>
+        <v>3.079540329053998e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.259959046568838e-07</v>
+        <v>6.590075827261899e-07</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.820021395815274e-07</v>
+        <v>7.028940672171302e-06</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.255430034547317e-09</v>
+        <v>2.567756610005745e-06</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.486227104891441e-08</v>
+        <v>1.957136191776954e-06</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.865912472951095e-08</v>
+        <v>2.941364073194563e-05</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.495934457007024e-09</v>
+        <v>2.975795041493257e-06</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.340666244686872e-09</v>
+        <v>7.689490303164348e-06</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.771653460191374e-08</v>
+        <v>1.573624831507914e-05</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.558970966352717e-08</v>
+        <v>2.860735094145639e-06</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.044552071036378e-08</v>
+        <v>5.889869498787448e-06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.422722218398121e-07</v>
+        <v>3.429134267207701e-06</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.721034395695824e-08</v>
+        <v>4.956902557751164e-06</v>
       </c>
       <c r="BL2" t="n">
-        <v>8.229254433445021e-08</v>
+        <v>5.473024430102669e-06</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.238813721078259e-07</v>
+        <v>3.767670477827778e-06</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.814810162732329e-09</v>
+        <v>7.942278898553923e-06</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.992725497591891e-08</v>
+        <v>1.958264874701854e-07</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.262942816993018e-08</v>
+        <v>1.317982605542056e-05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.409004539709713e-07</v>
+        <v>1.077830006579461e-06</v>
       </c>
       <c r="BR2" t="n">
-        <v>3.755904742774874e-08</v>
+        <v>8.712504495633766e-06</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.477111766234884e-08</v>
+        <v>4.975524461769965e-06</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.140598702269017e-08</v>
+        <v>2.789430027405615e-06</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.517048506931133e-08</v>
+        <v>1.676112333370838e-06</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.880042646007496e-07</v>
+        <v>2.791400766000152e-05</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.590424574260396e-07</v>
+        <v>2.535995463404106e-06</v>
       </c>
       <c r="BX2" t="n">
-        <v>4.241361395429522e-08</v>
+        <v>7.322522833419498e-06</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.242949470598887e-08</v>
+        <v>1.758603389134805e-06</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.525668551494164e-07</v>
+        <v>2.069501169899013e-05</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.621363178917818e-08</v>
+        <v>5.428523763839621e-06</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.148355378039923e-07</v>
+        <v>7.941343028505798e-06</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.784868241041295e-08</v>
+        <v>3.702230515045812e-06</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.049240859809288e-08</v>
+        <v>3.92966876461287e-06</v>
       </c>
       <c r="CE2" t="n">
-        <v>6.169895527818881e-08</v>
+        <v>7.843047569622286e-06</v>
       </c>
       <c r="CF2" t="n">
-        <v>9.889660645967524e-09</v>
+        <v>2.657900040503591e-06</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.745476296832749e-08</v>
+        <v>5.116777401781292e-07</v>
       </c>
       <c r="CH2" t="n">
-        <v>5.273279590767288e-09</v>
+        <v>3.318041308375541e-06</v>
       </c>
       <c r="CI2" t="n">
-        <v>6.041400268941288e-08</v>
+        <v>8.511519808962476e-06</v>
       </c>
       <c r="CJ2" t="n">
-        <v>6.410837727344187e-08</v>
+        <v>5.943098130956059e-06</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.006660568236839e-07</v>
+        <v>2.198148507659425e-07</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.856097853192296e-08</v>
+        <v>2.117169515258865e-06</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.00963565180723e-09</v>
+        <v>4.674905085266801e-06</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.097270623835357e-07</v>
+        <v>1.505847740190802e-05</v>
       </c>
       <c r="CO2" t="n">
-        <v>7.617920516622689e-09</v>
+        <v>3.441213323185366e-07</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.201439374654001e-07</v>
+        <v>7.948411621327978e-06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.168225125525169e-07</v>
+        <v>2.154465164494468e-06</v>
       </c>
       <c r="CR2" t="n">
-        <v>7.375248856078542e-08</v>
+        <v>1.356765278615057e-05</v>
       </c>
       <c r="CS2" t="n">
-        <v>8.709616849955637e-08</v>
+        <v>7.564874522358878e-07</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.656246150285369e-08</v>
+        <v>9.367041684527067e-07</v>
       </c>
       <c r="CU2" t="n">
-        <v>2.779343422076863e-10</v>
+        <v>5.581308869295754e-06</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.679589134440107e-09</v>
+        <v>6.6720781433105e-06</v>
       </c>
       <c r="CW2" t="n">
-        <v>9.938823097854765e-08</v>
+        <v>8.70336498337565e-06</v>
       </c>
       <c r="CX2" t="n">
-        <v>8.603796786132989e-09</v>
+        <v>2.481106093910057e-06</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.84374799264242e-08</v>
+        <v>3.080302803937229e-06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.119000974687424e-08</v>
+        <v>4.798144800588489e-06</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.244020637614085e-07</v>
+        <v>9.835132914304268e-06</v>
       </c>
       <c r="DB2" t="n">
-        <v>4.524864749555491e-08</v>
+        <v>2.664188741619e-06</v>
       </c>
       <c r="DC2" t="n">
-        <v>8.725741196258241e-08</v>
+        <v>3.155034278279345e-07</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.413098793534573e-08</v>
+        <v>1.320154638051463e-06</v>
       </c>
       <c r="DE2" t="n">
-        <v>9.777405551858465e-09</v>
+        <v>1.028450515150325e-05</v>
       </c>
       <c r="DF2" t="n">
-        <v>3.266955559411144e-07</v>
+        <v>3.920461040252121e-06</v>
       </c>
       <c r="DG2" t="n">
-        <v>7.027539794535187e-08</v>
+        <v>8.439577868557535e-06</v>
       </c>
       <c r="DH2" t="n">
-        <v>2.495097817245551e-07</v>
+        <v>5.543010956898797e-07</v>
       </c>
       <c r="DI2" t="n">
-        <v>1.693491356036247e-07</v>
+        <v>7.048132374620764e-06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>6.280107101019894e-08</v>
+        <v>7.446875315508805e-06</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.063686028146549e-07</v>
+        <v>9.340496035292745e-06</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.652840779797771e-07</v>
+        <v>1.615919586583914e-06</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.172445820429857e-07</v>
+        <v>7.478963198082056e-06</v>
       </c>
       <c r="DN2" t="n">
-        <v>6.493948490060575e-08</v>
+        <v>3.034014980585198e-06</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.579068905106396e-07</v>
+        <v>1.979559783649165e-06</v>
       </c>
       <c r="DP2" t="n">
-        <v>8.011401320118239e-09</v>
+        <v>1.899182962006307e-06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>4.916660145681817e-08</v>
+        <v>4.379952770250384e-06</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.29045576563658e-07</v>
+        <v>8.894162419892382e-06</v>
       </c>
       <c r="DS2" t="n">
-        <v>1.107057556737345e-07</v>
+        <v>8.835176231514197e-06</v>
       </c>
       <c r="DT2" t="n">
-        <v>4.883450088755126e-08</v>
+        <v>6.203970315254992e-08</v>
       </c>
       <c r="DU2" t="n">
-        <v>9.942279177721502e-08</v>
+        <v>6.118304554547649e-06</v>
       </c>
       <c r="DV2" t="n">
-        <v>1.043890307528272e-08</v>
+        <v>1.135522325057536e-06</v>
       </c>
       <c r="DW2" t="n">
-        <v>6.761730020343748e-08</v>
+        <v>3.997000476374524e-06</v>
       </c>
       <c r="DX2" t="n">
-        <v>5.993578611196426e-08</v>
+        <v>8.482600605930202e-06</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.688616511179134e-08</v>
+        <v>4.976736818207428e-07</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.827337570148302e-08</v>
+        <v>6.423055310733616e-06</v>
       </c>
       <c r="EA2" t="n">
-        <v>3.860625952256669e-08</v>
+        <v>5.215587407292333e-06</v>
       </c>
       <c r="EB2" t="n">
-        <v>6.508466299237625e-08</v>
+        <v>1.159208295575809e-05</v>
       </c>
       <c r="EC2" t="n">
-        <v>7.943227586793e-08</v>
+        <v>1.774503857632226e-06</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.412049073223898e-07</v>
+        <v>5.444943326438079e-06</v>
       </c>
       <c r="EE2" t="n">
-        <v>7.815376790176742e-08</v>
+        <v>2.47978414336103e-06</v>
       </c>
       <c r="EF2" t="n">
-        <v>2.96749345096714e-08</v>
+        <v>1.930629650814808e-06</v>
       </c>
       <c r="EG2" t="n">
-        <v>5.477125952779716e-08</v>
+        <v>3.787649120567949e-06</v>
       </c>
       <c r="EH2" t="n">
-        <v>4.41492247205133e-08</v>
+        <v>2.414870436950878e-07</v>
       </c>
       <c r="EI2" t="n">
-        <v>4.680432397208278e-08</v>
+        <v>2.770381797745358e-06</v>
       </c>
       <c r="EJ2" t="n">
-        <v>5.307413886157519e-08</v>
+        <v>5.399263500294182e-06</v>
       </c>
       <c r="EK2" t="n">
-        <v>3.415997795741532e-08</v>
+        <v>1.560459736538178e-06</v>
       </c>
       <c r="EL2" t="n">
-        <v>1.042189481381683e-07</v>
+        <v>1.536135414426099e-06</v>
       </c>
       <c r="EM2" t="n">
-        <v>4.623387539481882e-08</v>
+        <v>1.550329102428805e-06</v>
       </c>
       <c r="EN2" t="n">
-        <v>3.705250861685272e-08</v>
+        <v>3.510458554956131e-06</v>
       </c>
       <c r="EO2" t="n">
-        <v>1.28257422460365e-08</v>
+        <v>2.537451109674294e-06</v>
       </c>
       <c r="EP2" t="n">
-        <v>2.334736670661641e-08</v>
+        <v>1.067996981873875e-05</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1.060800514096627e-07</v>
+        <v>3.873794867104152e-06</v>
       </c>
       <c r="ER2" t="n">
-        <v>4.969614053607074e-09</v>
+        <v>1.771804818417877e-06</v>
       </c>
       <c r="ES2" t="n">
-        <v>2.734078634603065e-07</v>
+        <v>2.342833795410115e-06</v>
       </c>
       <c r="ET2" t="n">
-        <v>6.901714044715845e-08</v>
+        <v>2.387027109307382e-07</v>
       </c>
       <c r="EU2" t="n">
-        <v>8.593045208726835e-08</v>
+        <v>3.267655756644672e-06</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.840608945258282e-07</v>
+        <v>8.149448262884107e-07</v>
       </c>
       <c r="EW2" t="n">
-        <v>1.018471493807738e-07</v>
+        <v>2.446083726681536e-06</v>
       </c>
       <c r="EX2" t="n">
-        <v>4.068511749721893e-09</v>
+        <v>5.17436728841858e-06</v>
       </c>
       <c r="EY2" t="n">
-        <v>3.742580290122532e-08</v>
+        <v>9.338196832686663e-06</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1.377867242524644e-08</v>
+        <v>1.312247491114249e-06</v>
       </c>
       <c r="FA2" t="n">
-        <v>1.426169582430248e-08</v>
+        <v>2.695557441256824e-06</v>
       </c>
       <c r="FB2" t="n">
-        <v>5.898710853102784e-08</v>
+        <v>2.774012045847485e-06</v>
       </c>
       <c r="FC2" t="n">
-        <v>6.884622649749872e-08</v>
+        <v>8.929853720474057e-06</v>
       </c>
       <c r="FD2" t="n">
-        <v>7.737300222743215e-08</v>
+        <v>7.063335942802951e-06</v>
       </c>
       <c r="FE2" t="n">
-        <v>7.38162242441831e-08</v>
+        <v>5.296620884109871e-07</v>
       </c>
       <c r="FF2" t="n">
-        <v>8.16683609627944e-09</v>
+        <v>1.157705696641642e-06</v>
       </c>
       <c r="FG2" t="n">
-        <v>1.834609619777439e-08</v>
+        <v>1.734410716380808e-06</v>
       </c>
       <c r="FH2" t="n">
-        <v>3.78772462283905e-08</v>
+        <v>8.429687113675755e-06</v>
       </c>
       <c r="FI2" t="n">
-        <v>1.352596825654473e-07</v>
+        <v>3.222148734494112e-06</v>
       </c>
       <c r="FJ2" t="n">
-        <v>9.60648662839958e-08</v>
+        <v>8.492545020999387e-06</v>
       </c>
       <c r="FK2" t="n">
-        <v>2.777139229692693e-08</v>
+        <v>7.077845111780334e-06</v>
       </c>
       <c r="FL2" t="n">
-        <v>2.846418567514775e-08</v>
+        <v>1.109668914978101e-06</v>
       </c>
       <c r="FM2" t="n">
-        <v>2.193038284303839e-08</v>
+        <v>7.036714123387355e-06</v>
       </c>
       <c r="FN2" t="n">
-        <v>4.503096917574112e-08</v>
+        <v>2.135260274371831e-06</v>
       </c>
       <c r="FO2" t="n">
-        <v>2.446398461586341e-08</v>
+        <v>1.825434765123646e-06</v>
       </c>
       <c r="FP2" t="n">
-        <v>2.111479702193719e-08</v>
+        <v>3.580284555937396e-06</v>
       </c>
       <c r="FQ2" t="n">
-        <v>4.206960113606328e-08</v>
+        <v>7.286311301868409e-06</v>
       </c>
       <c r="FR2" t="n">
-        <v>3.429601491689027e-09</v>
+        <v>1.018486000248231e-05</v>
       </c>
       <c r="FS2" t="n">
-        <v>1.629369705824502e-07</v>
+        <v>2.597792627057061e-05</v>
       </c>
       <c r="FT2" t="n">
-        <v>2.465821751229669e-07</v>
+        <v>1.122284174925881e-05</v>
       </c>
       <c r="FU2" t="n">
-        <v>1.738282833230187e-07</v>
+        <v>1.200485348817892e-05</v>
       </c>
       <c r="FV2" t="n">
-        <v>7.390681133756516e-08</v>
+        <v>1.615714063518681e-05</v>
       </c>
       <c r="FW2" t="n">
-        <v>1.948827588194035e-08</v>
+        <v>8.964208291217801e-07</v>
       </c>
       <c r="FX2" t="n">
-        <v>4.08113720595793e-08</v>
+        <v>4.794073902303353e-06</v>
       </c>
       <c r="FY2" t="n">
-        <v>6.723224643678805e-09</v>
+        <v>1.986799588848953e-06</v>
       </c>
       <c r="FZ2" t="n">
-        <v>7.024968340374471e-08</v>
+        <v>1.643818222873961e-06</v>
       </c>
       <c r="GA2" t="n">
-        <v>4.972743994358098e-08</v>
+        <v>1.134137392000412e-06</v>
       </c>
       <c r="GB2" t="n">
-        <v>1.553807749132829e-08</v>
+        <v>4.156858267378993e-06</v>
       </c>
       <c r="GC2" t="n">
-        <v>4.919705816064379e-07</v>
+        <v>3.717680101544829e-06</v>
       </c>
       <c r="GD2" t="n">
-        <v>2.021386258377333e-08</v>
+        <v>3.7790700844198e-06</v>
       </c>
       <c r="GE2" t="n">
-        <v>9.941985723571634e-08</v>
+        <v>8.124669875542168e-06</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.665472382228472e-08</v>
+        <v>3.35553022523527e-06</v>
       </c>
       <c r="GG2" t="n">
-        <v>3.705685003296821e-08</v>
+        <v>2.023115939664422e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0008215091074816883</v>
+        <v>2.361168299103156e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.007357816211879253</v>
+        <v>0.0005069130565971136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007596974610351026</v>
+        <v>0.0001795350108295679</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002901285421103239</v>
+        <v>0.0002098018449032679</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001185678644105792</v>
+        <v>1.854811853263527e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003822124563157558</v>
+        <v>0.0005148540949448943</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000451955886092037</v>
+        <v>4.986057319911197e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002513336483389139</v>
+        <v>0.0002314954035682604</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008211316308006644</v>
+        <v>0.0001216529490193352</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00168187078088522</v>
+        <v>0.0001035200548358262</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006597218103706837</v>
+        <v>0.0005949715850874782</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003580268821679056</v>
+        <v>0.0002499231486581266</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002426447346806526</v>
+        <v>0.0004454495501704514</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001952547172550112</v>
+        <v>0.0002209945232607424</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003576611168682575</v>
+        <v>0.0006037885323166847</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003313964116387069</v>
+        <v>4.679514313465916e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006102535990066826</v>
+        <v>7.011048728600144e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001637006178498268</v>
+        <v>0.0001259000127902254</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003023514873348176</v>
+        <v>0.0001028400292852893</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007793501717969775</v>
+        <v>4.836438165511936e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.000668381922878325</v>
+        <v>6.479662260971963e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004772191459778696</v>
+        <v>4.498981797951274e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005813061725348234</v>
+        <v>9.0493616880849e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001130633638240397</v>
+        <v>0.0001262586301891133</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0004888223484158516</v>
+        <v>0.000115302660560701</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001270859269425273</v>
+        <v>0.0001290798682020977</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001157693914137781</v>
+        <v>7.350792293436825e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0004067051340825856</v>
+        <v>6.624336674576625e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0004819438909180462</v>
+        <v>2.709173713810742e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.651000638958067e-05</v>
+        <v>9.595199662726372e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>7.823276973795146e-05</v>
+        <v>0.0001256077375728637</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0008778382325544953</v>
+        <v>0.0001428814139217138</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0003365974698681384</v>
+        <v>0.0002142470475519076</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.000314327422529459</v>
+        <v>3.422261215746403e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.000212902610655874</v>
+        <v>0.0003720480599440634</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0005985636962577701</v>
+        <v>2.369873436691705e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0007691995706409216</v>
+        <v>9.070755913853645e-05</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.001172114629298449</v>
+        <v>6.020470027578995e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0001489598944317549</v>
+        <v>5.082981078885496e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0007968096761032939</v>
+        <v>8.072535274550319e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0002859412925317883</v>
+        <v>0.0001110259108827449</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0009501046733930707</v>
+        <v>8.928793977247551e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0005664450582116842</v>
+        <v>2.505390693841036e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0001220673584612086</v>
+        <v>8.149011409841478e-05</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.001031357096508145</v>
+        <v>6.865069735795259e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0005972487851977348</v>
+        <v>0.0001192790296045132</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.004268782213330269</v>
+        <v>0.0004193305503576994</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0003024619072675705</v>
+        <v>0.000161472344188951</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.000675296294502914</v>
+        <v>0.0001261488650925457</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0003070602251682431</v>
+        <v>0.0004223840369377285</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.003067437093704939</v>
+        <v>0.0004671081260312349</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.002042683074250817</v>
+        <v>1.783812695066445e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.001134681515395641</v>
+        <v>8.002384856808931e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002112460788339376</v>
+        <v>1.033380976878107e-05</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0005722347996197641</v>
+        <v>0.0001262123550986871</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.00128172873519361</v>
+        <v>2.683610728126951e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.001583439647220075</v>
+        <v>0.0001276154507650062</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0002794331812765449</v>
+        <v>0.0001322798780165613</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0008011817699298263</v>
+        <v>0.0002016730722971261</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0005111470818519592</v>
+        <v>6.226840196177363e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.000876224716193974</v>
+        <v>4.01230608986225e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.00128467008471489</v>
+        <v>0.0002573454694356769</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.001478591118939221</v>
+        <v>6.507713987957686e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0002639266895130277</v>
+        <v>2.632092946441844e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0007923795492388308</v>
+        <v>0.0001428815448889509</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0007976455963216722</v>
+        <v>5.200373561820015e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.533224950544536e-05</v>
+        <v>9.874247189145535e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0001940045331139117</v>
+        <v>0.0001209231413668022</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0005466399015858769</v>
+        <v>7.09518208168447e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0008900591637939215</v>
+        <v>9.490567026659846e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0007337903371080756</v>
+        <v>8.161296136677265e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.813314833678305e-05</v>
+        <v>8.107542817015201e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.08155722450465e-06</v>
+        <v>7.68398167565465e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.002433221088722348</v>
+        <v>0.0001625911827431992</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.001224022707901895</v>
+        <v>3.023509634658694e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0002091674832627177</v>
+        <v>4.858869942836463e-06</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0005235119024291635</v>
+        <v>3.40317128575407e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.001480267150327563</v>
+        <v>0.000246440147748217</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0003995225997641683</v>
+        <v>0.000181739596882835</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0003558454918675125</v>
+        <v>5.946312376181595e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0009209542768076062</v>
+        <v>9.500309533905238e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0001468190748710185</v>
+        <v>1.288792736886535e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.001312564476393163</v>
+        <v>0.0001655761443544179</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0006458446732722223</v>
+        <v>5.597477138508111e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0001545480045024306</v>
+        <v>4.660504782805219e-05</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002390662557445467</v>
+        <v>4.7318622819148e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0003412157238926739</v>
+        <v>0.0001290224900003523</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.000555011909455061</v>
+        <v>9.572506314725615e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0005050198524259031</v>
+        <v>2.894245517381933e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0006179085467010736</v>
+        <v>5.926540325162932e-07</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001559398369863629</v>
+        <v>6.446013867389411e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0002937455428764224</v>
+        <v>5.944474833086133e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>3.583227953640744e-05</v>
+        <v>0.0001833692804211751</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.002599035855382681</v>
+        <v>0.000131472508655861</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0006276926142163575</v>
+        <v>8.936096855904907e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.0009578306926414371</v>
+        <v>5.406925993156619e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.00154670502524823</v>
+        <v>0.0001602765842108056</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.001143148168921471</v>
+        <v>0.000236167325056158</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0004399843164719641</v>
+        <v>0.0001049040656653233</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0001482634979765862</v>
+        <v>5.488972965395078e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.001282103592529893</v>
+        <v>0.000141042226459831</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0006782902637496591</v>
+        <v>7.862330676289275e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0005645649507641792</v>
+        <v>7.207577436929569e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0003633728192653507</v>
+        <v>5.295799928717315e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0002311684074811637</v>
+        <v>0.0001679480192251503</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0005277460440993309</v>
+        <v>2.975814277306199e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0008844244293868542</v>
+        <v>3.088625817326829e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0005930714542046189</v>
+        <v>9.534956916468218e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0008343485533259809</v>
+        <v>1.014861663861666e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0006092777475714684</v>
+        <v>0.0001996315259020776</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0004233690269757062</v>
+        <v>0.0001691967772785574</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.001156477024778724</v>
+        <v>0.0001031243882607669</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.001250251661986113</v>
+        <v>2.946358472399879e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.003813724033534527</v>
+        <v>0.0001469608250772581</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0006673276657238603</v>
+        <v>1.592321677890141e-05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.001813372480683029</v>
+        <v>0.0002006993163377047</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.001558636082336307</v>
+        <v>4.118921788176522e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>2.334002056159079e-05</v>
+        <v>5.153475649422035e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.0006259322399273515</v>
+        <v>0.0001198892714455724</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.0007168910815380514</v>
+        <v>3.115959771093912e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>4.751826782012358e-05</v>
+        <v>0.0001183942731586285</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0004305627080611885</v>
+        <v>6.550193575094454e-06</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.001276345225051045</v>
+        <v>9.324280836153775e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.001376683358103037</v>
+        <v>0.000108953652670607</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.000288891838863492</v>
+        <v>0.0002086389577016234</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.0001010065025184304</v>
+        <v>8.024144335649908e-05</v>
       </c>
       <c r="DW3" t="n">
-        <v>6.435421528294683e-05</v>
+        <v>9.370094630867243e-06</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0007772127282805741</v>
+        <v>5.969551421003416e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.000683779246173799</v>
+        <v>0.000173809879925102</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.001013372908346355</v>
+        <v>3.559144715836737e-06</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0004152124165557325</v>
+        <v>0.0001500970683991909</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.000545650371350348</v>
+        <v>2.175756162614562e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0004468656843528152</v>
+        <v>0.0001604059507371858</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0001848116371547803</v>
+        <v>0.0001592575281392783</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.001598475617356598</v>
+        <v>0.0001985089620575309</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0005698305321857333</v>
+        <v>1.529207656858489e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.001432370045222342</v>
+        <v>1.874964073067531e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0005487552843987942</v>
+        <v>2.974247763631865e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0003158509207423776</v>
+        <v>5.237366349319927e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.000407946587074548</v>
+        <v>4.416456795297563e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.001170337316580117</v>
+        <v>4.906339017907158e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.0009162219939753413</v>
+        <v>3.75697563868016e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0003119456523563713</v>
+        <v>2.771158688119613e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0002561459550634027</v>
+        <v>0.0001035262685036287</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0001874671434052289</v>
+        <v>5.508178946911357e-05</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0008519500261172652</v>
+        <v>0.0001177641388494521</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0009522722102701664</v>
+        <v>7.061517680995166e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.0003711887402459979</v>
+        <v>0.0001281744334846735</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.001207914901897311</v>
+        <v>6.693473551422358e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0005253757699392736</v>
+        <v>0.0001364735799143091</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.001730679767206311</v>
+        <v>2.924345608334988e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.001975083723664284</v>
+        <v>3.99424388888292e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0003197209734935313</v>
+        <v>2.414841765130404e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0003268037107773125</v>
+        <v>4.036410973640159e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.001200464088469744</v>
+        <v>0.000181354145752266</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0005563810700550675</v>
+        <v>4.441983764991164e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>1.240198616869748e-05</v>
+        <v>9.121783659793437e-05</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0002984690072480589</v>
+        <v>4.217864261590876e-05</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.0001476836914662272</v>
+        <v>0.0001293058594455943</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.0009641296928748488</v>
+        <v>1.555617927806452e-05</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.0007885682862251997</v>
+        <v>2.631771531014238e-05</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0008531216299161315</v>
+        <v>3.487666617729701e-05</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.0002685680228751153</v>
+        <v>9.244085958926007e-06</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0004212309431750327</v>
+        <v>7.253210060298443e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.001085583702661097</v>
+        <v>0.0001024126977426931</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.001376043073832989</v>
+        <v>0.0001129777883761562</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.0004222843563184142</v>
+        <v>1.84786222234834e-05</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.0004832374979741871</v>
+        <v>0.0001790795067790896</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.0005190055817365646</v>
+        <v>4.13148918596562e-05</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.000526027986779809</v>
+        <v>0.000123851903481409</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.0008158473065122962</v>
+        <v>0.0002751050051301718</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0008496994851157069</v>
+        <v>0.0001100521330954507</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.0001778975711204112</v>
+        <v>0.0001060959839378484</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0007066731341183186</v>
+        <v>1.917616464197636e-05</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.001005546771921217</v>
+        <v>7.538063800893724e-05</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.0004911533906124532</v>
+        <v>4.125521081732586e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.001013282453641295</v>
+        <v>5.533142029889859e-05</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.001066962257027626</v>
+        <v>0.0001398139720549807</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.000961143639869988</v>
+        <v>0.0004502097144722939</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0006661137449555099</v>
+        <v>9.299379598814994e-06</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.001504588406533003</v>
+        <v>6.750159082002938e-05</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.0005232733092270792</v>
+        <v>9.309287997893989e-05</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0005885412101633847</v>
+        <v>0.0002356324694119394</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.0002604089095257223</v>
+        <v>4.595626523951069e-05</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.0009951444808393717</v>
+        <v>0.0002855887578334659</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.0004141477693337947</v>
+        <v>0.0001653600193094462</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.001735927420668304</v>
+        <v>5.797818448627368e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.0005707900272682309</v>
+        <v>5.293959839036688e-05</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0002111555077135563</v>
+        <v>1.0623922207742e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.01861057803034782</v>
+        <v>7.691685459576547e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2371256947517395</v>
+        <v>0.0003072718100156635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006445686332881451</v>
+        <v>8.086328307399526e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1187348589301109</v>
+        <v>0.000139282681629993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0323340892791748</v>
+        <v>2.964583836728707e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.203238770365715</v>
+        <v>0.0002460949181113392</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001469207927584648</v>
+        <v>7.335331611102447e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08297643065452576</v>
+        <v>5.382629024097696e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01685802266001701</v>
+        <v>2.620859049784485e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04856201261281967</v>
+        <v>6.06481044087559e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2230824679136276</v>
+        <v>0.0003722988767549396</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004515244159847498</v>
+        <v>3.619294875534251e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08597143739461899</v>
+        <v>0.0002394993061898276</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003100891131907701</v>
+        <v>0.0001041201467160136</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1893228590488434</v>
+        <v>0.0003065447090193629</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01312901824712753</v>
+        <v>1.62144388013985e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03677046671509743</v>
+        <v>5.395979678723961e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005585072096437216</v>
+        <v>5.801376391900703e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01078718341886997</v>
+        <v>2.669899913598783e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01615801453590393</v>
+        <v>3.404895687708631e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02153419330716133</v>
+        <v>3.690987796289846e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03197560459375381</v>
+        <v>3.376134191057645e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0583316832780838</v>
+        <v>1.433596480637789e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0186696108430624</v>
+        <v>4.896780956187285e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01893303729593754</v>
+        <v>3.684147304738872e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05739665031433105</v>
+        <v>0.0001411184493917972</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03486910462379456</v>
+        <v>8.815244655124843e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001438789069652557</v>
+        <v>6.378634134307504e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0133759044110775</v>
+        <v>3.182239743182436e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.009325931780040264</v>
+        <v>2.891817348427139e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.009861024096608162</v>
+        <v>7.368098886217922e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01389772724360228</v>
+        <v>7.501863001380116e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0143308974802494</v>
+        <v>9.57558659138158e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.01284622400999069</v>
+        <v>1.038577920553507e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.008509773761034012</v>
+        <v>0.0002094470110023394</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0130384424701333</v>
+        <v>3.103895505773835e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02094356715679169</v>
+        <v>7.265630119945854e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04187099635601044</v>
+        <v>3.806336462730542e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002297541126608849</v>
+        <v>3.82097132387571e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.008399352431297302</v>
+        <v>3.109603494522162e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0009102043695747852</v>
+        <v>3.698737600643653e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.02807123400270939</v>
+        <v>4.573251771944342e-06</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00256158341653645</v>
+        <v>3.918401489499956e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01317024976015091</v>
+        <v>0.000139212075737305</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.02483553253114223</v>
+        <v>2.128598316630814e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.03235190361738205</v>
+        <v>0.0001164827408501878</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1736998409032822</v>
+        <v>0.0002425203565508127</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.005375235341489315</v>
+        <v>6.464351463364437e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04496053233742714</v>
+        <v>6.902298628119752e-05</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.01709465309977531</v>
+        <v>0.0001876322639873251</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1077655255794525</v>
+        <v>0.0001726334303384647</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.02394679933786392</v>
+        <v>5.942084499110933e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0204777829349041</v>
+        <v>8.392642484977841e-06</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.06129929423332214</v>
+        <v>4.703050944954157e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0216589942574501</v>
+        <v>1.221837555931415e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.03791249915957451</v>
+        <v>5.933384090894833e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.04754414781928062</v>
+        <v>1.650933700148016e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00249142711982131</v>
+        <v>0.0001169502138509415</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03823554515838623</v>
+        <v>7.435803854605183e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.06128839775919914</v>
+        <v>5.427400537882932e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.01917595602571964</v>
+        <v>2.736876922426745e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.01999368704855442</v>
+        <v>8.326924580615014e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.01394461281597614</v>
+        <v>5.294046422932297e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0001503666862845421</v>
+        <v>1.321857234870549e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0546487532556057</v>
+        <v>3.645935066742823e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.00672224722802639</v>
+        <v>1.886590212052397e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.01508929952979088</v>
+        <v>6.962921179365367e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003939978778362274</v>
+        <v>2.317588041478302e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001912229578010738</v>
+        <v>1.05286089819856e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.01697306707501411</v>
+        <v>0.000124360216432251</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.006471746601164341</v>
+        <v>1.833459464251064e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.006727925501763821</v>
+        <v>8.065887232078239e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01539248321205378</v>
+        <v>3.784135333262384e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.09007550776004791</v>
+        <v>0.0001345257624052465</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.01483060978353024</v>
+        <v>2.049492104561068e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.03765137121081352</v>
+        <v>6.383928848663345e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02255133725702763</v>
+        <v>3.248325811000541e-06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.04176545515656471</v>
+        <v>8.927455201046541e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.01393814291805029</v>
+        <v>3.400472633074969e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0002313493750989437</v>
+        <v>2.527182368794456e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.04003608599305153</v>
+        <v>4.524458199739456e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001381583511829376</v>
+        <v>1.066539516614284e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.03101350367069244</v>
+        <v>9.209743438987061e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.02275220118463039</v>
+        <v>3.784714863286354e-06</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.01631583645939827</v>
+        <v>3.520170139381662e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.005913358181715012</v>
+        <v>1.502861596236471e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0315823070704937</v>
+        <v>8.074149081949145e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.01641953736543655</v>
+        <v>2.530566962377634e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.01131806336343288</v>
+        <v>1.880705167423002e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.02083336561918259</v>
+        <v>3.772290074266493e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.05034342035651207</v>
+        <v>3.250980807933956e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.007730855606496334</v>
+        <v>9.80980257736519e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.005318635143339634</v>
+        <v>8.703589264769107e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0362873338162899</v>
+        <v>0.0001225228043040261</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001192907337099314</v>
+        <v>2.261467670905404e-06</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.006107674911618233</v>
+        <v>8.500288822688162e-05</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.04923717677593231</v>
+        <v>5.848703949595802e-06</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.04619910195469856</v>
+        <v>0.0001025323872454464</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.009500612504780293</v>
+        <v>3.769935574382544e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0001195187214761972</v>
+        <v>2.348103953409009e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.02730012498795986</v>
+        <v>8.889888704288751e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.01881650649011135</v>
+        <v>1.058936959452694e-06</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02870979718863964</v>
+        <v>5.380349466577172e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.007997095584869385</v>
+        <v>1.63135991897434e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03324554488062859</v>
+        <v>8.741121564526111e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01652374491095543</v>
+        <v>5.449879608931951e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.02352634444832802</v>
+        <v>2.382257298449986e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.01090287044644356</v>
+        <v>3.269608714617789e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.005340783856809139</v>
+        <v>2.506393684598152e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.01120668277144432</v>
+        <v>5.012480323784985e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.007310524582862854</v>
+        <v>4.254374653100967e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.08527781814336777</v>
+        <v>1.193059233628446e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04483778774738312</v>
+        <v>0.0001924586395034567</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02795918844640255</v>
+        <v>8.084376895567402e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.004713171161711216</v>
+        <v>5.913638233323582e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.03878370299935341</v>
+        <v>1.742140739224851e-06</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.02164205349981785</v>
+        <v>2.927568857558072e-06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.004920377396047115</v>
+        <v>3.202759035048075e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0031406763009727</v>
+        <v>6.178076728247106e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.01693795807659626</v>
+        <v>1.819178214645945e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0004337313584983349</v>
+        <v>5.311001586960629e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.008421801961958408</v>
+        <v>2.330850657017436e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002283880952745676</v>
+        <v>2.551390934968367e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.00104664801619947</v>
+        <v>5.983177834423259e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002834649290889502</v>
+        <v>0.0001228998880833387</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.02057269774377346</v>
+        <v>4.802750481758267e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0001513669267296791</v>
+        <v>3.133450445602648e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0252188928425312</v>
+        <v>1.87354235094972e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.01928079500794411</v>
+        <v>3.274233677075244e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.008103316649794579</v>
+        <v>4.372009425424039e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.00138934375718236</v>
+        <v>6.830459460616112e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01551226247102022</v>
+        <v>4.313945100875571e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0007104217074811459</v>
+        <v>3.700749584822915e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.004836912266910076</v>
+        <v>6.078441219870001e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0101972296833992</v>
+        <v>7.395865395665169e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.01348243094980717</v>
+        <v>2.134999022018746e-06</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.03572700917720795</v>
+        <v>2.157592825824395e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.01130735781043768</v>
+        <v>3.755558282136917e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.007187223993241787</v>
+        <v>1.986643837881275e-06</v>
       </c>
       <c r="EJ4" t="n">
-        <v>8.202483877539635e-05</v>
+        <v>1.140911626862362e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.02313658222556114</v>
+        <v>2.899988248827867e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.01592731103301048</v>
+        <v>1.62789237947436e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.006859187036752701</v>
+        <v>6.775162091798848e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.01097701955586672</v>
+        <v>1.743659959174693e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.001153502613306046</v>
+        <v>3.267017018515617e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.01492869574576616</v>
+        <v>4.102702951058745e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01754457503557205</v>
+        <v>4.007309325970709e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.02199815027415752</v>
+        <v>4.721219738712534e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.01740813255310059</v>
+        <v>4.862611240241677e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02959133125841618</v>
+        <v>6.817911344114691e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.03905221074819565</v>
+        <v>2.747707912931219e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.06678984314203262</v>
+        <v>4.716587864095345e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.005901198834180832</v>
+        <v>4.893737786915153e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.004123020451515913</v>
+        <v>2.409339685982559e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.02567833662033081</v>
+        <v>0.0001116581843234599</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0155309671536088</v>
+        <v>1.008548451864044e-06</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.02027012594044209</v>
+        <v>6.7401364503894e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.004942032974213362</v>
+        <v>3.361576091265306e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02759478241205215</v>
+        <v>6.965905777178705e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.02859637886285782</v>
+        <v>1.932503073476255e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.01527217030525208</v>
+        <v>2.0131274141022e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.02188032492995262</v>
+        <v>1.615869223314803e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.01078008860349655</v>
+        <v>2.069177753583062e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.007210119161754847</v>
+        <v>0.0001290930085815489</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.01567903906106949</v>
+        <v>7.44444114388898e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03749755769968033</v>
+        <v>9.857016993919387e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.008984709158539772</v>
+        <v>4.490958963287994e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01825453341007233</v>
+        <v>0.0001205470762215555</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0005547641776502132</v>
+        <v>1.38623763632495e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.01815658807754517</v>
+        <v>7.851590635254979e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.01698459312319756</v>
+        <v>6.700785888824612e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.01559801958501339</v>
+        <v>1.580220487085171e-05</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.03934814780950546</v>
+        <v>3.913992986781523e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.03251191973686218</v>
+        <v>0.0001950183359440416</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0003659832291305065</v>
+        <v>3.248353459639475e-05</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.004876871593296528</v>
+        <v>0.0001110694793169387</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01117378659546375</v>
+        <v>1.0976964404108e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.02655639685690403</v>
+        <v>3.012898014276288e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.004022484645247459</v>
+        <v>2.379688339715358e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.01491651218384504</v>
+        <v>1.347186116618104e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.04654818028211594</v>
+        <v>1.862807766883634e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.01586588658392429</v>
+        <v>6.941500760149211e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.02829737588763237</v>
+        <v>6.398886034730822e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.01245159562677145</v>
+        <v>1.255087590834592e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.01304948329925537</v>
+        <v>0.0001825021317927167</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.01801168918609619</v>
+        <v>8.525674638804048e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.1004845723509789</v>
+        <v>2.506627606635448e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.001938051544129848</v>
+        <v>3.56614327756688e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.004058975260704756</v>
+        <v>2.736289025051519e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.000144314777571708</v>
+        <v>9.684785027275211e-07</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001869396190159023</v>
+        <v>5.619906914944295e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001237125543411821</v>
+        <v>4.913781594950706e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000392859656130895</v>
+        <v>1.713130131975049e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004673385119531304</v>
+        <v>2.78321499536105e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0004175872600171715</v>
+        <v>8.052302291616797e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000289405114017427</v>
+        <v>2.796407898131292e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002337529003852978</v>
+        <v>5.58515966986306e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002795870532281697</v>
+        <v>5.080403298052261e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002041987463599071</v>
+        <v>5.367971880332334e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001648076227866113</v>
+        <v>6.849195415270515e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>4.456980605027638e-06</v>
+        <v>2.680597390281036e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002343781525269151</v>
+        <v>4.080195594724501e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>7.928599370643497e-05</v>
+        <v>6.673756161035271e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003300730313640088</v>
+        <v>1.065810465661343e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001585933787282556</v>
+        <v>1.781623495844542e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001919291680678725</v>
+        <v>3.687071966851363e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003656261833384633</v>
+        <v>1.2646103186853e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>8.659066224936396e-05</v>
+        <v>1.97168361637523e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002210674429079518</v>
+        <v>4.724053042082232e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>6.789417966501787e-05</v>
+        <v>1.110426183004165e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001651412167120725</v>
+        <v>6.557239657922764e-07</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002051943447440863</v>
+        <v>9.018548894346168e-07</v>
       </c>
       <c r="X7" t="n">
-        <v>6.040728112566285e-05</v>
+        <v>1.340832113783108e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.820397821778897e-05</v>
+        <v>8.903189154807478e-07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003487916255835444</v>
+        <v>2.789565314742504e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001241104037035257</v>
+        <v>7.29408384358976e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000136229646159336</v>
+        <v>1.666501248109853e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0001441746426280588</v>
+        <v>1.679826482359204e-07</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.813095877878368e-05</v>
+        <v>1.801201676698838e-07</v>
       </c>
       <c r="AE7" t="n">
-        <v>9.937054710462689e-05</v>
+        <v>2.139785920007853e-06</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.070603194530122e-05</v>
+        <v>1.874179702099354e-06</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.553246955969371e-05</v>
+        <v>1.961207090062089e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.011488974560052e-05</v>
+        <v>3.803770027843711e-07</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.951438263058662e-05</v>
+        <v>4.753524990519509e-06</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.024465306429192e-05</v>
+        <v>1.498428218837944e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0003018919960595667</v>
+        <v>7.092679084053088e-07</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0001816431031329557</v>
+        <v>1.90117475540319e-07</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.401021604076959e-05</v>
+        <v>1.454897073926986e-07</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001500809448771179</v>
+        <v>3.587396406601329e-07</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0001624881697352976</v>
+        <v>1.036801222653594e-06</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.00012848453479819</v>
+        <v>6.078618071114761e-07</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0001283932651858777</v>
+        <v>2.119687110280211e-07</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.588609666214325e-05</v>
+        <v>2.395747287664562e-06</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0001367280056001619</v>
+        <v>3.810362727563188e-07</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.662845119833946e-05</v>
+        <v>1.187052134810074e-06</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.001121829729527235</v>
+        <v>7.045618986012414e-06</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0001618846436031163</v>
+        <v>9.731909358379198e-07</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.812497981125489e-05</v>
+        <v>9.906088962452486e-07</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.229076436487958e-05</v>
+        <v>3.979099801654229e-06</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0001172524498542771</v>
+        <v>6.843269147793762e-06</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0004197589005343616</v>
+        <v>4.955153372065979e-07</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0001679434790275991</v>
+        <v>2.002920837185229e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0001625605946173891</v>
+        <v>6.427679863918456e-07</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.578893665689975e-05</v>
+        <v>6.186841119415476e-07</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0002903149579651654</v>
+        <v>1.137914978244225e-06</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0002992796071339399</v>
+        <v>1.311314008489717e-06</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.877493721432984e-05</v>
+        <v>2.303259634572896e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.000282326975138858</v>
+        <v>1.731100155666354e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0002185789489885792</v>
+        <v>1.686076274154402e-07</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.221756873652339e-05</v>
+        <v>7.477868848582148e-07</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002228934463346377</v>
+        <v>4.259712113707792e-06</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0003162974899169058</v>
+        <v>4.206711423648812e-08</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001090959849534556</v>
+        <v>7.330048390485899e-08</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0001654686639085412</v>
+        <v>2.32239881370333e-06</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.707854895968921e-05</v>
+        <v>7.285259471245809e-07</v>
       </c>
       <c r="BO7" t="n">
-        <v>8.407361747231334e-05</v>
+        <v>1.977221018023556e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>8.476828952552751e-05</v>
+        <v>1.441351173525618e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.976757787109818e-05</v>
+        <v>8.206473012251081e-07</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001225361338583753</v>
+        <v>1.970964149222709e-06</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.372489143454004e-05</v>
+        <v>1.100851250157575e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.294339932035655e-05</v>
+        <v>1.889286750156316e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.47357417922467e-05</v>
+        <v>2.328087873593176e-07</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0006513716070912778</v>
+        <v>3.262189466113341e-06</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0001497179036960006</v>
+        <v>7.506096153520048e-07</v>
       </c>
       <c r="BX7" t="n">
-        <v>8.579660061514005e-05</v>
+        <v>1.223093363478256e-06</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.057842594804242e-05</v>
+        <v>1.550179490550363e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>8.509851795679424e-06</v>
+        <v>3.292037717983476e-06</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.072478234069422e-05</v>
+        <v>5.93773108903406e-07</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.524679414113052e-06</v>
+        <v>1.619275508346618e-06</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.377466029836796e-05</v>
+        <v>3.921083191471553e-08</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.167060877894983e-05</v>
+        <v>6.817296593908395e-08</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0003189050767105073</v>
+        <v>1.539155846330686e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>6.631863652728498e-05</v>
+        <v>3.818142886302667e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.623439235729165e-05</v>
+        <v>9.637009270591079e-07</v>
       </c>
       <c r="CH7" t="n">
-        <v>6.810612831031904e-05</v>
+        <v>8.825053328109789e-07</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.166157835541526e-05</v>
+        <v>2.222833472842467e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0001224772859131917</v>
+        <v>6.137962600405444e-07</v>
       </c>
       <c r="CK7" t="n">
-        <v>5.08287557750009e-05</v>
+        <v>3.518284188430698e-07</v>
       </c>
       <c r="CL7" t="n">
-        <v>8.686283399583772e-05</v>
+        <v>8.774790671850496e-07</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0004538365465123206</v>
+        <v>5.230546662460256e-08</v>
       </c>
       <c r="CN7" t="n">
-        <v>6.880261935293674e-05</v>
+        <v>3.010694854310714e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>7.271065260283649e-05</v>
+        <v>2.52499125963368e-06</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0005464509013108909</v>
+        <v>4.111414909857558e-06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0003382407012395561</v>
+        <v>7.907331109890947e-07</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0004243392031639814</v>
+        <v>1.965241608559154e-06</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0003089748206548393</v>
+        <v>5.525971573661081e-07</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0001630076149012893</v>
+        <v>1.867475816652586e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0002466056030243635</v>
+        <v>4.395261328227207e-07</v>
       </c>
       <c r="CV7" t="n">
-        <v>7.479024498024955e-05</v>
+        <v>2.268551355655291e-07</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0003035457921214402</v>
+        <v>1.296880554946256e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>6.857843982288614e-05</v>
+        <v>4.113815634809725e-07</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0001324387994827703</v>
+        <v>1.352280833089026e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>9.321765537606552e-05</v>
+        <v>9.975418606700259e-07</v>
       </c>
       <c r="DA7" t="n">
-        <v>3.159762491122819e-05</v>
+        <v>2.628138872751151e-06</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0001223819999722764</v>
+        <v>1.381135206202089e-09</v>
       </c>
       <c r="DC7" t="n">
-        <v>9.424450399819762e-05</v>
+        <v>2.94321893079541e-07</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001018870752886869</v>
+        <v>5.485295559992664e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0001602504344191402</v>
+        <v>3.065380838052079e-07</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0002697846502996981</v>
+        <v>2.980675617436646e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0001060251670423895</v>
+        <v>1.428810946890735e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0002537966065574437</v>
+        <v>9.656830002313654e-08</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0005414252518676221</v>
+        <v>1.950915248016827e-06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0007134765619412065</v>
+        <v>2.240873754999484e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.012119411025196e-05</v>
+        <v>8.315998911712086e-07</v>
       </c>
       <c r="DL7" t="n">
-        <v>9.285258420277387e-05</v>
+        <v>4.079189466210664e-07</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0004017963947262615</v>
+        <v>8.594325890953769e-07</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0001132622419390827</v>
+        <v>4.153641555149079e-07</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0001103864924516529</v>
+        <v>2.482081811194803e-07</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0001525800325907767</v>
+        <v>5.82933012083231e-07</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0001601546246092767</v>
+        <v>5.600585382126155e-07</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.784319313941523e-05</v>
+        <v>3.761632569876383e-07</v>
       </c>
       <c r="DS7" t="n">
-        <v>8.210854139178991e-05</v>
+        <v>1.434299576885678e-07</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0002380119840381667</v>
+        <v>1.502299028288689e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0001968070573639125</v>
+        <v>2.710315811782493e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0001036545509123243</v>
+        <v>4.086997762442479e-07</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.389646710478701e-05</v>
+        <v>4.012409817732987e-07</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0002336534962523729</v>
+        <v>5.699266125702707e-07</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.561427289852872e-05</v>
+        <v>7.213426442831405e-07</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0002411552704870701</v>
+        <v>2.286475819346379e-06</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.000179271912202239</v>
+        <v>1.259161081179627e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>6.672294693998992e-05</v>
+        <v>1.215090833284194e-06</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.868046042043716e-05</v>
+        <v>6.004449915053556e-08</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0001862592907855287</v>
+        <v>1.30082480609417e-06</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0003856640250887722</v>
+        <v>2.496816705388483e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0002549297641962767</v>
+        <v>1.703787262385958e-07</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0004440037009771913</v>
+        <v>7.792694418640167e-07</v>
       </c>
       <c r="EH7" t="n">
-        <v>2.573709934949875e-05</v>
+        <v>7.194722684289445e-07</v>
       </c>
       <c r="EI7" t="n">
-        <v>1.034650631481782e-05</v>
+        <v>5.608408741863968e-07</v>
       </c>
       <c r="EJ7" t="n">
-        <v>4.685897238232428e-06</v>
+        <v>9.080452514353965e-07</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0002432379842502996</v>
+        <v>1.606322939551319e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.000168841754202731</v>
+        <v>5.279367201183049e-07</v>
       </c>
       <c r="EM7" t="n">
-        <v>9.037042764248326e-05</v>
+        <v>3.415898675029894e-07</v>
       </c>
       <c r="EN7" t="n">
-        <v>2.785430297080893e-05</v>
+        <v>1.324608405184335e-07</v>
       </c>
       <c r="EO7" t="n">
-        <v>8.689709648024291e-05</v>
+        <v>4.805992261935899e-07</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0001167322843684815</v>
+        <v>2.043582526312093e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0001265308383153751</v>
+        <v>1.157423412223579e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0001812790287658572</v>
+        <v>6.484280561380729e-07</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0001911258441396058</v>
+        <v>2.65766459506267e-07</v>
       </c>
       <c r="ET7" t="n">
-        <v>1.449551928089932e-05</v>
+        <v>1.72747377291671e-06</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.000333867414155975</v>
+        <v>9.894220056594349e-07</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0002429642336210236</v>
+        <v>3.351842678966932e-07</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0001060033100657165</v>
+        <v>6.103690566305886e-07</v>
       </c>
       <c r="EX7" t="n">
-        <v>9.93850699160248e-05</v>
+        <v>2.63361073393753e-07</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0003124684153590351</v>
+        <v>2.125008450093446e-06</v>
       </c>
       <c r="EZ7" t="n">
-        <v>5.056027293903753e-05</v>
+        <v>1.711809005655596e-07</v>
       </c>
       <c r="FA7" t="n">
-        <v>2.398886499577202e-05</v>
+        <v>1.616353529243497e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>6.406837928807363e-05</v>
+        <v>7.178064151958097e-07</v>
       </c>
       <c r="FC7" t="n">
-        <v>9.515457350062206e-06</v>
+        <v>2.286097696924116e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0001864988298621029</v>
+        <v>5.653748758049915e-07</v>
       </c>
       <c r="FE7" t="n">
-        <v>7.94623265392147e-05</v>
+        <v>1.38033925622949e-07</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0001460718340240419</v>
+        <v>1.819516910472885e-07</v>
       </c>
       <c r="FG7" t="n">
-        <v>9.368343307869509e-05</v>
+        <v>1.619992673340676e-07</v>
       </c>
       <c r="FH7" t="n">
-        <v>9.774856880540028e-05</v>
+        <v>1.995362936213496e-06</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0001715690596029162</v>
+        <v>1.335662318524555e-06</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0002771826984826475</v>
+        <v>1.018633497551491e-06</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0001200075348606333</v>
+        <v>2.397688149358146e-06</v>
       </c>
       <c r="FL7" t="n">
-        <v>3.753237979253754e-05</v>
+        <v>2.278970214319997e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0001360860042041168</v>
+        <v>1.277662249776768e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>7.71599734434858e-05</v>
+        <v>1.766970285643765e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0001498602796345949</v>
+        <v>2.901727384596597e-06</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0002710186818148941</v>
+        <v>5.705722969651106e-07</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0001263443264178932</v>
+        <v>5.009051733395609e-07</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0002092294016620144</v>
+        <v>2.896080559366965e-06</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0002723265788517892</v>
+        <v>1.40922225000395e-06</v>
       </c>
       <c r="FT7" t="n">
-        <v>3.111476326012053e-05</v>
+        <v>3.967805696447613e-06</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0002428536681691185</v>
+        <v>6.030808208379312e-08</v>
       </c>
       <c r="FV7" t="n">
-        <v>7.982909301063046e-05</v>
+        <v>1.474039947879646e-07</v>
       </c>
       <c r="FW7" t="n">
-        <v>8.873403203324415e-07</v>
+        <v>4.079403879586607e-06</v>
       </c>
       <c r="FX7" t="n">
-        <v>8.96219426067546e-05</v>
+        <v>1.870885739663208e-07</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0003071661340072751</v>
+        <v>6.232333475963969e-07</v>
       </c>
       <c r="FZ7" t="n">
-        <v>8.165003237081692e-05</v>
+        <v>1.641509925320861e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>6.751508772140369e-05</v>
+        <v>2.432717565170606e-06</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.665238960413262e-05</v>
+        <v>6.315553946478758e-08</v>
       </c>
       <c r="GC7" t="n">
-        <v>9.690553997643292e-05</v>
+        <v>3.058127049371251e-06</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0001629586913622916</v>
+        <v>2.686270363483345e-06</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.806791988201439e-05</v>
+        <v>2.506860141693323e-07</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0001598936360096559</v>
+        <v>6.981475735301501e-07</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0001296707923756912</v>
+        <v>7.436117925863073e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.00167021865490824</v>
+        <v>0.0002845706476364285</v>
       </c>
       <c r="B8" t="n">
-        <v>9.457235137233511e-05</v>
+        <v>4.116450145374984e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001039326598402113</v>
+        <v>0.0003513158881105483</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004113095346838236</v>
+        <v>4.370500391814858e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>8.604559843661264e-05</v>
+        <v>0.0002429278974886984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001741273095831275</v>
+        <v>0.0001889189588837326</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002676239528227597</v>
+        <v>0.0001904700766317546</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008560880087316036</v>
+        <v>9.807941387407482e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.276838469901122e-05</v>
+        <v>5.51759876543656e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001234577037394047</v>
+        <v>0.0002218269655713812</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001699691492831334</v>
+        <v>0.0001012149587040767</v>
       </c>
       <c r="L8" t="n">
-        <v>2.443724952172488e-05</v>
+        <v>0.000335507036652416</v>
       </c>
       <c r="M8" t="n">
-        <v>0.000219470530282706</v>
+        <v>4.957719647791237e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000489481317345053</v>
+        <v>0.0002134509268216789</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001377980457618833</v>
+        <v>0.0003517789882607758</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0006541566690430045</v>
+        <v>0.0001557462674099952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.000984865939244628</v>
+        <v>7.422069029416889e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001051660001394339</v>
+        <v>6.483511242549866e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001898791088024154</v>
+        <v>9.546357614453882e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0005104299052618444</v>
+        <v>0.0002309273986611515</v>
       </c>
       <c r="U8" t="n">
-        <v>3.203335654688999e-05</v>
+        <v>0.0001406455994583666</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004628211027011275</v>
+        <v>0.0001050041464623064</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006969345267862082</v>
+        <v>0.0001612154010217637</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0003153313009534031</v>
+        <v>0.0001811901020118967</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0003236066550016403</v>
+        <v>6.176505848998204e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0001597583468537778</v>
+        <v>2.815273910528049e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.049503958318383e-05</v>
+        <v>2.70626405836083e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0003404128656256944</v>
+        <v>5.058411989011802e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0003432836092542857</v>
+        <v>9.519295417703688e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0001445720554329455</v>
+        <v>2.093514922307804e-06</v>
       </c>
       <c r="AE8" t="n">
-        <v>9.105939534492791e-05</v>
+        <v>4.054516466567293e-06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.436747697880492e-05</v>
+        <v>5.25549694430083e-07</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002059012185782194</v>
+        <v>4.096018892596476e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.703036105027422e-05</v>
+        <v>8.404911932302639e-05</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0002679356839507818</v>
+        <v>2.126984327333048e-05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.354572593001649e-05</v>
+        <v>4.749907020595856e-05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0003242402744945139</v>
+        <v>1.497523044236004e-05</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.94378322805278e-05</v>
+        <v>0.0001532843452878296</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.000275331549346447</v>
+        <v>6.919736188137904e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.000114569251309149</v>
+        <v>6.246727571124211e-05</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0001353005063720047</v>
+        <v>5.806615081382915e-05</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.333595668664202e-05</v>
+        <v>2.330707502551377e-05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001418007013853639</v>
+        <v>7.192896009655669e-05</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.619181269546971e-05</v>
+        <v>5.161129956832156e-05</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.997238905460108e-05</v>
+        <v>4.475112655200064e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0009070850792340934</v>
+        <v>2.136469083779957e-05</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.000221832815441303</v>
+        <v>3.331449261168018e-05</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.402916137129068e-06</v>
+        <v>0.0001664221053943038</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0004851377452723682</v>
+        <v>7.248120527947322e-05</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001159089268185198</v>
+        <v>7.020934572210535e-05</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0007836536387912929</v>
+        <v>0.0001953776954906061</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.000214110070373863</v>
+        <v>5.746536407968961e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0004195109358988702</v>
+        <v>0.0001765969209372997</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.156238719588146e-05</v>
+        <v>6.356993981171399e-05</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000372301583411172</v>
+        <v>0.0002097870601573959</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0001624443248147145</v>
+        <v>7.369628292508423e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.064738696906716e-05</v>
+        <v>4.100907972315326e-06</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.000129853084217757</v>
+        <v>2.306440728716552e-05</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0003903942997567356</v>
+        <v>6.98645890224725e-05</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0003902594035025686</v>
+        <v>9.912991663441062e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0003353790671098977</v>
+        <v>7.871654815971851e-05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0004055915051139891</v>
+        <v>0.000183473268407397</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.783356805797666e-05</v>
+        <v>1.36747785290936e-05</v>
       </c>
       <c r="BL8" t="n">
-        <v>2.205625605711248e-05</v>
+        <v>0.0001067290431819856</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0002696837473195046</v>
+        <v>8.782050281297415e-05</v>
       </c>
       <c r="BN8" t="n">
-        <v>9.568194218445569e-05</v>
+        <v>0.0001613433560123667</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0004294213431421667</v>
+        <v>0.0001256528194062412</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0003837457334157079</v>
+        <v>0.0001683606387814507</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.100034857401624e-05</v>
+        <v>1.770026574376971e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0003631241852417588</v>
+        <v>1.418005194864236e-05</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0004840173642151058</v>
+        <v>5.979699926683679e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.000231667043408379</v>
+        <v>2.733158544288017e-05</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0004505117249209434</v>
+        <v>3.774874494411051e-05</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.000261965295067057</v>
+        <v>0.000199053916730918</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.000180715651367791</v>
+        <v>0.0001503590756328776</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0002590147196315229</v>
+        <v>7.558496145065874e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005098658730275929</v>
+        <v>0.0001156370781245641</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.000585670059081167</v>
+        <v>0.000233451573876664</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.707853804575279e-05</v>
+        <v>7.526332410634495e-06</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0001970465818885714</v>
+        <v>2.223123556177597e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.544131737318821e-05</v>
+        <v>3.954645217163488e-05</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0003249882720410824</v>
+        <v>6.48438508505933e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0002376708289375529</v>
+        <v>0.0001357399742119014</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.394972034380771e-05</v>
+        <v>7.506688416469842e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>1.570706444908865e-05</v>
+        <v>8.179075666703284e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>3.818058030446991e-05</v>
+        <v>5.263241473585367e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0002575337130110711</v>
+        <v>5.190487354411744e-05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.672460686881095e-05</v>
+        <v>4.671094757213723e-06</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0003021221491508186</v>
+        <v>3.474405821179971e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>3.335371002322063e-05</v>
+        <v>2.136584225809202e-05</v>
       </c>
       <c r="CM8" t="n">
-        <v>3.04564819089137e-05</v>
+        <v>2.517998109397013e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>8.544472802896053e-05</v>
+        <v>6.703023245790973e-05</v>
       </c>
       <c r="CO8" t="n">
-        <v>5.306265666149557e-05</v>
+        <v>7.228417962323874e-05</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.838301043084357e-05</v>
+        <v>4.121501842746511e-05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0007699021953158081</v>
+        <v>6.838799163233489e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0001226038439199328</v>
+        <v>3.489452501526102e-05</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0002251061087008566</v>
+        <v>0.0001264276797883213</v>
       </c>
       <c r="CT8" t="n">
-        <v>6.472003587987274e-05</v>
+        <v>4.855604493059218e-05</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001393267011735588</v>
+        <v>1.282876110053621e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0002993880480062217</v>
+        <v>6.743473204551265e-05</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0002217972651124001</v>
+        <v>9.504622721578926e-05</v>
       </c>
       <c r="CX8" t="n">
-        <v>4.503293166635558e-05</v>
+        <v>6.342241249512881e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>9.8626253020484e-05</v>
+        <v>7.703118171775714e-05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>3.361049311934039e-05</v>
+        <v>4.523683310253546e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0002509529876988381</v>
+        <v>5.475396028487012e-05</v>
       </c>
       <c r="DB8" t="n">
-        <v>9.168230462819338e-06</v>
+        <v>2.578637941041961e-05</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.000317820260534063</v>
+        <v>1.031508782034507e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.331703944946639e-05</v>
+        <v>9.382628377352376e-06</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0001015603847918101</v>
+        <v>8.372783486265689e-05</v>
       </c>
       <c r="DF8" t="n">
-        <v>4.186153091723099e-06</v>
+        <v>2.029938332270831e-05</v>
       </c>
       <c r="DG8" t="n">
-        <v>8.462984260404482e-05</v>
+        <v>8.753647853154689e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0002712910354603082</v>
+        <v>9.287933062296361e-05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001021156320348382</v>
+        <v>0.0001209652400575578</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0001048705671564676</v>
+        <v>6.690370355499908e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.082425923319533e-05</v>
+        <v>3.196422039764002e-05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0004910093848593533</v>
+        <v>3.395717430976219e-05</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0003435872786212713</v>
+        <v>1.992621764657088e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0001932077575474977</v>
+        <v>3.052259125979617e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>9.108742233365774e-05</v>
+        <v>5.519985643331893e-05</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0001477284531574696</v>
+        <v>0.0001550452725496143</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0002956194803118706</v>
+        <v>0.0001169196766568348</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0002545712632127106</v>
+        <v>4.054810415254906e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0002335230819880962</v>
+        <v>0.0001163043634733185</v>
       </c>
       <c r="DT8" t="n">
-        <v>1.033703301800415e-05</v>
+        <v>4.192177584627643e-05</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0004397512238938361</v>
+        <v>7.888139407441486e-06</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0001359848247375339</v>
+        <v>7.391051894956036e-06</v>
       </c>
       <c r="DW8" t="n">
-        <v>2.156382834073156e-06</v>
+        <v>4.963086030329578e-05</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.000174379616510123</v>
+        <v>4.447580795385875e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.831164450384676e-06</v>
+        <v>0.0002256112347822636</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001053648957167752</v>
+        <v>0.0001201660998049192</v>
       </c>
       <c r="EA8" t="n">
-        <v>6.966355431359261e-05</v>
+        <v>2.728130129980855e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004054703167639673</v>
+        <v>0.0001241442805621773</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0002119124983437359</v>
+        <v>2.072961251542438e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.000367523287422955</v>
+        <v>2.55653740168782e-05</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001539886288810521</v>
+        <v>1.925789547385648e-06</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0002663191989995539</v>
+        <v>3.364745498402044e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0004039595078211278</v>
+        <v>0.0001899069757200778</v>
       </c>
       <c r="EH8" t="n">
-        <v>1.525594143458875e-05</v>
+        <v>1.849455293267965e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001829966640798375</v>
+        <v>5.304724982124753e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0001377759617753327</v>
+        <v>0.0001031080755637959</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0001358421868644655</v>
+        <v>6.546754775627051e-06</v>
       </c>
       <c r="EL8" t="n">
-        <v>4.225572774885222e-05</v>
+        <v>2.999361277034041e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>1.93957475858042e-05</v>
+        <v>4.254993109498173e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>6.253326864680275e-05</v>
+        <v>3.496760837151669e-05</v>
       </c>
       <c r="EO8" t="n">
-        <v>9.829392365645617e-05</v>
+        <v>4.722438825410791e-05</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0003070847596973181</v>
+        <v>0.0001221645652549341</v>
       </c>
       <c r="EQ8" t="n">
-        <v>7.616166840307415e-05</v>
+        <v>6.350100011331961e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.000132653716718778</v>
+        <v>1.293811146751978e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0004557844949886203</v>
+        <v>3.061180905206129e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>8.481410623062402e-05</v>
+        <v>0.0001446355890948325</v>
       </c>
       <c r="EU8" t="n">
-        <v>2.369064895901829e-05</v>
+        <v>4.393735434859991e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>6.031319935573265e-05</v>
+        <v>0.0001642536517465487</v>
       </c>
       <c r="EW8" t="n">
-        <v>2.31600170081947e-05</v>
+        <v>4.494047607295215e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0002573538513388485</v>
+        <v>5.405039701145142e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0001832035486586392</v>
+        <v>9.381685958942398e-05</v>
       </c>
       <c r="EZ8" t="n">
-        <v>4.149982851231471e-05</v>
+        <v>5.841600795974955e-05</v>
       </c>
       <c r="FA8" t="n">
-        <v>7.206894224509597e-05</v>
+        <v>9.20398160815239e-05</v>
       </c>
       <c r="FB8" t="n">
-        <v>7.042604556772858e-05</v>
+        <v>6.559869507327676e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0002192361571360379</v>
+        <v>8.444026752840728e-05</v>
       </c>
       <c r="FD8" t="n">
-        <v>5.375863838708028e-05</v>
+        <v>1.181417610496283e-05</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0004133410402573645</v>
+        <v>4.956786142429337e-06</v>
       </c>
       <c r="FF8" t="n">
-        <v>5.782567313872278e-07</v>
+        <v>3.482586180325598e-06</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001954740146175027</v>
+        <v>0.0001010437117656693</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0002578626153990626</v>
+        <v>5.009950837120414e-05</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.000141154756420292</v>
+        <v>3.099008608842269e-05</v>
       </c>
       <c r="FJ8" t="n">
-        <v>6.83922553434968e-05</v>
+        <v>6.718456279486418e-05</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0001891303836600855</v>
+        <v>0.000169078863109462</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0002186479250667617</v>
+        <v>0.0001702331937849522</v>
       </c>
       <c r="FM8" t="n">
-        <v>5.577541378443129e-05</v>
+        <v>5.207703361520544e-05</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0001239460834767669</v>
+        <v>0.000123813355457969</v>
       </c>
       <c r="FO8" t="n">
-        <v>6.068305083317682e-06</v>
+        <v>5.254218922345899e-05</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0001530023582745343</v>
+        <v>3.392765938770026e-05</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.00013038631004747</v>
+        <v>0.0002019608800765127</v>
       </c>
       <c r="FR8" t="n">
-        <v>1.128824078477919e-05</v>
+        <v>0.0002510814229026437</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0004744056495837867</v>
+        <v>2.407183637842536e-05</v>
       </c>
       <c r="FT8" t="n">
-        <v>2.861343455151655e-05</v>
+        <v>0.0003400120476726443</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0004335285630077124</v>
+        <v>5.441458051791415e-05</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.000273186044069007</v>
+        <v>0.0002336479956284165</v>
       </c>
       <c r="FW8" t="n">
-        <v>5.068710379418917e-05</v>
+        <v>8.208354120142758e-05</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0001207228560815565</v>
+        <v>0.00012780494580511</v>
       </c>
       <c r="FY8" t="n">
-        <v>7.045459642540663e-05</v>
+        <v>3.680904046632349e-05</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0002105933090206236</v>
+        <v>5.894929927308112e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>2.326890535186976e-05</v>
+        <v>0.0001227341126650572</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0001587430451763794</v>
+        <v>4.456578244571574e-05</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0001496007316745818</v>
+        <v>3.791035123867914e-05</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0003080392198171467</v>
+        <v>5.053302811575122e-05</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0002867106813937426</v>
+        <v>4.514684769674204e-05</v>
       </c>
       <c r="GF8" t="n">
-        <v>4.808702215086669e-06</v>
+        <v>0.0002294382429681718</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0001312531239818782</v>
+        <v>6.806275632698089e-05</v>
       </c>
     </row>
   </sheetData>
